--- a/survey_templates/047_group_class_popularity_assessment_form--survey_templates.xlsx
+++ b/survey_templates/047_group_class_popularity_assessment_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>class_frequency</t>
+          <t>class_frequency_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Class Frequency</t>
+          <t>Class Frequency 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Class Type</t>
+          <t>Class Type 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Class Level</t>
+          <t>Class Level 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Best Instructor</t>
+          <t>Best Instructor 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Class Duration</t>
+          <t>Class Duration 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Class Day</t>
+          <t>Class Day 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>class_frequency_2</t>
+          <t>class_frequency_2_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Class Frequency</t>
+          <t>Class Frequency 2 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,80 +1318,80 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>member_interest_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>member_interest_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>member_interest_choices</t>
+          <t>class_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pilates</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pilates</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>member_interest_choices</t>
+          <t>class_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yoga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yoga</t>
         </is>
       </c>
     </row>
@@ -1403,46 +1403,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pilates</t>
+          <t>zumba</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pilates</t>
+          <t>Zumba</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>class_type_choices</t>
+          <t>class_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yoga</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yoga</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>class_type_choices</t>
+          <t>class_level_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>zumba</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Zumba</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1454,46 +1454,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>class_level_choices</t>
+          <t>best_instructor_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>name_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Name 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>class_level_choices</t>
+          <t>best_instructor_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Name 2</t>
         </is>
       </c>
     </row>
@@ -1505,46 +1505,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>name_1</t>
+          <t>name_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Name 1</t>
+          <t>Name 3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>best_instructor_choices</t>
+          <t>class_day_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>name_2</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Name 2</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>best_instructor_choices</t>
+          <t>class_day_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>name_3</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Name 3</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1624,46 +1624,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>class_day_choices</t>
+          <t>class_duration_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>class_day_choices</t>
+          <t>class_duration_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -1692,97 +1692,97 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>class_duration_choices</t>
+          <t>class_frequency_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>class_duration_choices</t>
+          <t>class_frequency_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>class_frequency_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>class_type_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>pilates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Pilates</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>class_frequency_choices</t>
+          <t>class_type_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>yoga</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Yoga</t>
         </is>
       </c>
     </row>
@@ -1794,46 +1794,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pilates</t>
+          <t>zumba</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pilates</t>
+          <t>Zumba</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>class_type_2_choices</t>
+          <t>class_level_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>yoga</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yoga</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>class_type_2_choices</t>
+          <t>class_level_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>zumba</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Zumba</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1845,46 +1845,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>class_level_2_choices</t>
+          <t>best_instructor_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>name_1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Name 1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>class_level_2_choices</t>
+          <t>best_instructor_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Name 2</t>
         </is>
       </c>
     </row>
@@ -1896,46 +1896,46 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>name_1</t>
+          <t>name_3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Name 1</t>
+          <t>Name 3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>best_instructor_2_choices</t>
+          <t>class_duration_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>name_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Name 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>best_instructor_2_choices</t>
+          <t>class_duration_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>name_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Name 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1947,46 +1947,46 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>class_duration_2_choices</t>
+          <t>class_day_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>class_duration_2_choices</t>
+          <t>class_day_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -2066,95 +2066,61 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>class_day_2_choices</t>
+          <t>class_frequency_2_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>class_day_2_choices</t>
+          <t>class_frequency_2_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>class_frequency_2_choices</t>
+          <t>class_frequency_2_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>class_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>class_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
